--- a/warhammer_40k_chronology_audited_v4.xlsx
+++ b/warhammer_40k_chronology_audited_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Warhammer 40k\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE01BD0-16B2-41B4-860E-71C60712FBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7811AAD-CC18-4421-A85C-DEEA27B5C0E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5715" yWindow="3210" windowWidth="28830" windowHeight="17925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="315" yWindow="855" windowWidth="30870" windowHeight="17925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chronology_corrected" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="1195">
   <si>
     <t>Sort</t>
   </si>
@@ -3603,6 +3603,9 @@
   </si>
   <si>
     <t>Anthology internal short stories still require a separate story-level pass if you want every individual story disaggregated from anthology containers.</t>
+  </si>
+  <si>
+    <t>Смертельный огонь</t>
   </si>
 </sst>
 </file>
@@ -3634,13 +3637,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3890,7 +3893,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.5">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -3923,7 +3926,7 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="28.5">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -3956,7 +3959,7 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" ht="28.5">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -4022,7 +4025,7 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" ht="28.5">
-      <c r="A6" s="2">
+      <c r="A6" s="4">
         <v>35.200000000000003</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -4055,7 +4058,7 @@
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" ht="28.5">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>35.299999999999997</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4550,7 +4553,7 @@
       <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:11" ht="28.5">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -4583,7 +4586,7 @@
       <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:11" ht="28.5">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>58</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -4618,7 +4621,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="28.5">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -4651,7 +4654,7 @@
       <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:11" ht="28.5">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -4684,7 +4687,7 @@
       <c r="K25" s="2"/>
     </row>
     <row r="26" spans="1:11" ht="28.5">
-      <c r="A26" s="4">
+      <c r="A26" s="3">
         <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -4750,7 +4753,7 @@
       <c r="K27" s="2"/>
     </row>
     <row r="28" spans="1:11" ht="28.5">
-      <c r="A28" s="4">
+      <c r="A28" s="3">
         <v>72.5</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -4785,7 +4788,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="28.5">
-      <c r="A29" s="4">
+      <c r="A29" s="3">
         <v>75</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -4818,7 +4821,7 @@
       <c r="K29" s="2"/>
     </row>
     <row r="30" spans="1:11" ht="28.5">
-      <c r="A30" s="4">
+      <c r="A30" s="3">
         <v>80</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -4851,7 +4854,7 @@
       <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:11" ht="28.5">
-      <c r="A31" s="4">
+      <c r="A31" s="3">
         <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -4884,7 +4887,7 @@
       <c r="K31" s="2"/>
     </row>
     <row r="32" spans="1:11" ht="28.5">
-      <c r="A32" s="4">
+      <c r="A32" s="3">
         <v>85.5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -4919,7 +4922,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="28.5">
-      <c r="A33" s="4">
+      <c r="A33" s="3">
         <v>86</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -4952,7 +4955,7 @@
       <c r="K33" s="2"/>
     </row>
     <row r="34" spans="1:11" ht="42.75">
-      <c r="A34" s="4">
+      <c r="A34" s="3">
         <v>87</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -4987,7 +4990,7 @@
       </c>
     </row>
     <row r="35" spans="1:11" ht="42.75">
-      <c r="A35" s="4">
+      <c r="A35" s="3">
         <v>88</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -5022,7 +5025,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" ht="28.5">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>89.5</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -5055,7 +5058,7 @@
       <c r="K36" s="2"/>
     </row>
     <row r="37" spans="1:11" ht="28.5">
-      <c r="A37" s="4">
+      <c r="A37" s="3">
         <v>90</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -5088,7 +5091,7 @@
       <c r="K37" s="2"/>
     </row>
     <row r="38" spans="1:11" ht="28.5">
-      <c r="A38" s="4">
+      <c r="A38" s="3">
         <v>95</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -5133,7 +5136,9 @@
       <c r="D39" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" s="2" t="s">
+        <v>1194</v>
+      </c>
       <c r="F39" s="2" t="s">
         <v>23</v>
       </c>
@@ -5721,7 +5726,7 @@
       </c>
     </row>
     <row r="57" spans="1:11" ht="28.5">
-      <c r="A57" s="4">
+      <c r="A57" s="3">
         <v>145</v>
       </c>
       <c r="B57" s="2" t="s">
